--- a/test_samples/KUEHNE_NAGEL/sample2_ref.xlsx
+++ b/test_samples/KUEHNE_NAGEL/sample2_ref.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2205" yWindow="4140" windowWidth="28800" windowHeight="15315" tabRatio="819" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2550" yWindow="5370" windowWidth="28800" windowHeight="15510" tabRatio="819" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DWIHARTA" sheetId="1" state="visible" r:id="rId1"/>
@@ -50,7 +50,6 @@
       <name val="新細明體"/>
       <charset val="136"/>
       <family val="1"/>
-      <b val="1"/>
       <color theme="1"/>
       <sz val="12"/>
       <scheme val="minor"/>
@@ -84,7 +83,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -98,9 +97,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -510,21 +506,21 @@
   <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="17.375" customWidth="1" style="8" min="1" max="1"/>
-    <col width="15.75" customWidth="1" style="8" min="2" max="2"/>
-    <col width="29.5" customWidth="1" style="8" min="3" max="3"/>
-    <col width="26" customWidth="1" style="8" min="4" max="4"/>
-    <col width="25.5" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
-    <col width="17.875" customWidth="1" style="8" min="6" max="7"/>
-    <col width="29.25" customWidth="1" style="8" min="8" max="8"/>
-    <col width="13.75" customWidth="1" style="8" min="9" max="10"/>
-    <col width="17.625" customWidth="1" style="8" min="11" max="11"/>
-    <col width="20" customWidth="1" style="8" min="12" max="12"/>
-    <col width="16.875" bestFit="1" customWidth="1" style="8" min="13" max="13"/>
-    <col width="18.625" bestFit="1" customWidth="1" style="8" min="14" max="14"/>
-    <col width="16.375" customWidth="1" style="8" min="15" max="15"/>
-    <col width="7.625" bestFit="1" customWidth="1" style="8" min="16" max="16"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="8" min="17" max="17"/>
+    <col width="17.375" customWidth="1" style="7" min="1" max="1"/>
+    <col width="15.75" customWidth="1" style="7" min="2" max="2"/>
+    <col width="29.5" customWidth="1" style="7" min="3" max="3"/>
+    <col width="26" customWidth="1" style="7" min="4" max="4"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="17.875" customWidth="1" style="7" min="6" max="7"/>
+    <col width="29.25" customWidth="1" style="7" min="8" max="8"/>
+    <col width="13.75" customWidth="1" style="7" min="9" max="10"/>
+    <col width="17.625" customWidth="1" style="7" min="11" max="11"/>
+    <col width="20" customWidth="1" style="7" min="12" max="12"/>
+    <col width="16.875" bestFit="1" customWidth="1" style="7" min="13" max="13"/>
+    <col width="18.625" bestFit="1" customWidth="1" style="7" min="14" max="14"/>
+    <col width="16.375" customWidth="1" style="7" min="15" max="15"/>
+    <col width="7.625" bestFit="1" customWidth="1" style="7" min="16" max="16"/>
+    <col width="15.125" bestFit="1" customWidth="1" style="7" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customFormat="1" customHeight="1" s="1">
@@ -636,10 +632,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>28 Aug 2026</t>
-        </is>
+      <c r="A2" s="5" t="n">
+        <v>46262</v>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
@@ -664,23 +658,16 @@
       <c r="F2" s="4" t="n">
         <v>1521098</v>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>167321</v>
-      </c>
       <c r="H2" s="0" t="inlineStr">
         <is>
           <t>RYH0810096982</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>12 Oct 2026</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>23 Aug 2026</t>
-        </is>
+      <c r="I2" s="5" t="n">
+        <v>46307</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>46257</v>
       </c>
       <c r="K2" s="0" t="n">
         <v>1076554713</v>
@@ -695,7 +682,7 @@
           <t>JAKARTA</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>Los Angeles</t>
         </is>
@@ -720,9 +707,75 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
+      <c r="A3" s="5" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>CAK1131890</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>KUEHNE NAGEL INDONESIA</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>PT. POU YUEN INDONESIA</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n">
+        <v>167321</v>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>RYH0810096982</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>46307</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>46257</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>1076554713</v>
+      </c>
+      <c r="L3" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M3" s="0" t="inlineStr">
+        <is>
+          <t>JAKARTA</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="O3" s="0" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="P3" s="0" t="inlineStr">
+        <is>
+          <t>CMA CGM WHITE SHARK</t>
+        </is>
+      </c>
+      <c r="Q3" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R3" s="0" t="inlineStr">
+        <is>
+          <t>PT. POU YUEN INDONESIA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
@@ -749,9 +802,6 @@
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12">
       <c r="R12" s="1" t="n"/>
     </row>

--- a/test_samples/KUEHNE_NAGEL/sample2_ref.xlsx
+++ b/test_samples/KUEHNE_NAGEL/sample2_ref.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="P2" s="0" t="inlineStr">
         <is>
-          <t>CMA CGM WHITE SHARK</t>
+          <t>CMA CGM WHITE SHARK 0GVNQE1MA</t>
         </is>
       </c>
       <c r="Q2" s="0" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="P3" s="0" t="inlineStr">
         <is>
-          <t>CMA CGM WHITE SHARK</t>
+          <t>CMA CGM WHITE SHARK 0GVNQE1MA</t>
         </is>
       </c>
       <c r="Q3" s="0" t="inlineStr">
@@ -802,6 +802,9 @@
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
     </row>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12">
       <c r="R12" s="1" t="n"/>
     </row>

--- a/test_samples/KUEHNE_NAGEL/sample2_ref.xlsx
+++ b/test_samples/KUEHNE_NAGEL/sample2_ref.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2550" yWindow="5370" windowWidth="28800" windowHeight="15510" tabRatio="819" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DWIHARTA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DWIHARTA" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -725,6 +725,11 @@
           <t>PT. POU YUEN INDONESIA</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n">
         <v>167321</v>
